--- a/data_extactor/batch_10_fa/trimmed/batch_0040_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0040_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت شنوایی | به خاطرسپاری | درک کتبی | توجه شنیداری | چابکی انگشتان</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت شنوایی | حفظ کردن | درک کتبی | توجه شنیداری | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازیگران | استادان و مدرسان هنر، تئاتر و موسیقی در آموزش عالی | رقصندگان | دی‌جی‌ها (به‌جز رادیو) | مدیران موسیقی و آهنگسازان | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | مدرسان دوره‌های آزاد و مهارت‌آموزی شخصی</t>
+          <t>بازیگران | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | هنرمندان رقص و حرکات موزون | دی‌جی‌ها (به‌جز رادیو) | رهبران ارکستر، مدیران موسیقی و آهنگسازان | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,27 +555,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>دی‌جی کلوب | دی‌جی | دیسک‌جوکی | دی‌جی | دی‌جی مراسم و رویدادها | دی‌جی سیار | دی‌جی مهمانی | ترن‌تیبلیست | دی‌جی عروسی | دی‌جی برنامه‌های شبانه</t>
+          <t>دی‌جی کلوب | دی‌جی | دیسک‌جوکی | دی‌جی مراسم و رویدادها | دی‌جی سیار | دی‌جی مهمانی | ترن‌تیبلیست | دی‌جی عروسی | دی‌جی برنامه‌های شبانه</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Audition | Avid Technology Pro Tools | Audion Laboratories VoxPro | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Word</t>
+          <t>Adobe Audition | Avid Technology Pro Tools | Audion Laboratories VoxPro | نرم‌افزار Microsoft Office | Microsoft Word</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | مخابرات</t>
+          <t>هنرهای زیبا | خدمات مشتری و شخصی | ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | مخابرات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | چابکی انگشتان | توجه شنیداری | حساسیت شنوایی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | مهارت انگشتان | توجه شنیداری | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های صوت و تصویر | گویندگان پخش و مجریان رادیویی | مهمانداران و میزبانان سالن‌های پذیرایی | برنامه‌ریزان همایش‌ها، نشست‌ها و رویدادها | مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | تکنسین‌های صدابرداری و مهندسی صدا</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | گویندگان پخش و مجریان رادیویی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | رهبران ارکستر، مدیران موسیقی و آهنگسازان | نوازندگان و خوانندگان | تکنسین‌های مهندسی صدا</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتریان و خدمات فردی | فروش و بازاریابی | آموزش و پرورش | روان‌شناسی</t>
+          <t>هنرهای زیبا | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | فروش و بازاریابی | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | حساسیت به مسئله | ابتکار | هماهنگی عمومی بدن</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | اصالت | هماهنگی کلی بدن</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>بازیگران | رقصندگان | نوازندگان و خوانندگان | دی‌جی‌ها (به‌جز رادیو) | ورزشکاران و قهرمانان ورزشی | تهیه‌کنندگان و کارگردانان | کارشناسان و مربیان امور تفریحی</t>
+          <t>بازیگران | هنرمندان رقص و حرکات موزون | نوازندگان و خوانندگان | دی‌جی‌ها (به‌جز رادیو) | ورزشکاران و قهرمانان حرفه‌ای | تهیه‌کنندگان و کارگردانان | کارکنان و متصدیان امور تفریحی و اوقات فراغت</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | درک کتبی | ابتکار | روانی ایده‌ها</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | تشخیص گفتار | درک کتبی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازیگران | تکنسین‌های صوت و تصویر | تکنسین‌های پخش | دی‌جی‌ها (به‌جز رادیو) | مدیران پخش و برنامه‌ریزی رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | تهیه‌کنندگان و کارگردانان</t>
+          <t>بازیگران | تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | دی‌جی‌ها (به‌جز رادیو) | مدیران برنامه‌ریزی و پخش رسانه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | تهیه‌کنندگان و کارگردانان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | حقوق و مقررات دولتی | رایانه و الکترونیک | مخابرات | خدمات مشتریان و خدمات فردی | جغرافیا</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | قانون و دولت | رایانه و الکترونیک | مخابرات | خدمات مشتری و شخصی | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | درک کتبی | مرتب‌سازی اطلاعات | استدلال استقرایی</t>
+          <t>بیان شفاهی | درک شفاهی | بیان کتبی | وضوح گفتار | درک کتبی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>گویندگان پخش و مجریان رادیویی | استادان و مدرسان علوم ارتباطات در آموزش عالی | ویراستاران | تحلیل‌گران اطلاعاتی | شاعران، ترانه‌سرایان و نویسندگان خلاق | کارشناسان روابط عمومی | نویسندگان و پدیدآورندگان</t>
+          <t>گویندگان پخش و مجریان رادیویی | مدرسان علوم ارتباطات در دانشگاه‌ها و مراکز آموزش عالی | ویراستاران | تحلیل‌گران داده‌ها و اطلاعات امنیتی | شاعران، ترانه‌سرایان و نویسندگان خلاق | کارشناسان روابط عمومی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | فروش و بازاریابی | رایانه و الکترونیک</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان فروش تبلیغات | مدیران تبلیغات و روابط عمومی | مسئولان جذب منابع مالی و حامیان مالی | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | برنامه‌ریزان همایش‌ها، نشست‌ها و رویدادها | مدیران روابط عمومی | نویسندگان و پدیدآورندگان</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | مدیران تبلیغات و روابط ترویجی | کارشناسان جذب منابع مالی و حامی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مدیران روابط عمومی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | شنیدن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | نگارش | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | مدیریت و امور اداری | امور اداری و دفتری | آموزش و پرورش | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | مدیریت و اداره | اداری | آموزش و پرورش | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | دید نزدیک | ابتکار</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | بینایی نزدیک | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>صفحه‌آراها و ناشران رومیزی | متخصصان مدیریت اسناد و مدارک | طراحان گرافیک | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | نمونه‌خوانان و تصحیح‌کنندگان متون | نویسندگان متون فنی</t>
+          <t>متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | کارشناسان مدیریت اسناد و مدارک | طراحان گرافیک | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | ویراستاران فنی و نمونه‌خوان‌ها | نویسندگان متون فنی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | رایانه و الکترونیک | امور اداری و دفتری | ارتباطات و رسانه | مدیریت و امور اداری | تولید و فراوری</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | اداری | ارتباطات و رسانه | مدیریت و اداره | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | دید نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان کتبی | درک کتبی | بینایی نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>برنامه‌نویسان رایانه | تحلیل‌گران سیستم‌های رایانه‌ای | متخصصان مدیریت اسناد و مدارک | ویراستاران | مهندسان صنایع | نمونه‌خوانان و تصحیح‌کنندگان متون | نویسندگان و پدیدآورندگان</t>
+          <t>برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | کارشناسان مدیریت اسناد و مدارک | ویراستاران | مهندسان صنایع | ویراستاران فنی و نمونه‌خوان‌ها | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>فروش و بازاریابی | ارتباطات و رسانه | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | ابتکار | استدلال استقرایی</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | روانی ایده‌ها | اصالت | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران هنری | ویراستاران | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | نمونه‌خوانان و تصحیح‌کنندگان متون | کارشناسان روابط عمومی | نویسندگان متون فنی</t>
+          <t>مدیران هنری | ویراستاران | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | ویراستاران فنی و نمونه‌خوان‌ها | کارشناسان روابط عمومی | نویسندگان متون فنی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | شنیدن فعال</t>
+          <t>نگارش | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | امور اداری و دفتری | فروش و بازاریابی | هنرهای زیبا</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک | اداری | فروش و بازاریابی | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان کتبی | روانی ایده‌ها | درک کتبی | ابتکار | درک شفاهی | بیان شفاهی | استدلال استقرایی</t>
+          <t>بیان کتبی | روانی ایده‌ها | درک کتبی | اصالت | درک شفاهی | بیان شفاهی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>استادان و مدرسان هنر، تئاتر و موسیقی در آموزش عالی | ویراستاران | استادان و مدرسان زبان و ادبیات انگلیسی در آموزش عالی | مدیران موسیقی و آهنگسازان | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | تهیه‌کنندگان و کارگردانان | نویسندگان و پدیدآورندگان</t>
+          <t>مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | ویراستاران | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | رهبران ارکستر، مدیران موسیقی و آهنگسازان | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | تهیه‌کنندگان و کارگردانان | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
